--- a/Result/profitability/6220.xlsx
+++ b/Result/profitability/6220.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.1</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2300000000000001</v>
+        <v>0.1250000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>26.41625</v>
+        <v>26.01125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.45</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1462500000000001</v>
+        <v>0.1400000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>25.29375</v>
+        <v>24.84</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.45</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1612500000000001</v>
+        <v>0.2337500000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>23.8825</v>
+        <v>23.69125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-1.45</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0175000000000001</v>
+        <v>0.06375000000000011</v>
       </c>
       <c r="N5" t="n">
-        <v>21.5725</v>
+        <v>20.94125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.14</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0462500000000001</v>
+        <v>-0.0237499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>20.01375</v>
+        <v>19.22125</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.47</v>
       </c>
       <c r="M7" t="n">
-        <v>9.71445146547012e-17</v>
+        <v>-0.009999999999999898</v>
       </c>
       <c r="N7" t="n">
-        <v>18.715</v>
+        <v>18.18375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.83</v>
       </c>
       <c r="M8" t="n">
-        <v>0.05875000000000009</v>
+        <v>0.1337500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>17.2875</v>
+        <v>16.83125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -2026,7 +2026,7 @@
         <v>-0.08</v>
       </c>
       <c r="M13" t="n">
-        <v>0.415</v>
+        <v>0.4150000000000001</v>
       </c>
       <c r="N13" t="n">
         <v>19.62375</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6220</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2837</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2145</v>
+      </c>
+      <c r="E75" t="n">
+        <v>692</v>
+      </c>
+      <c r="F75" t="n">
+        <v>24.38</v>
+      </c>
+      <c r="G75" t="n">
+        <v>149</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>5.27%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-71</v>
+      </c>
+      <c r="J75" t="n">
+        <v>78</v>
+      </c>
+      <c r="K75" t="n">
+        <v>42</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.2775000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>27.84125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.875</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-3.650000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1302176239743134</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-4.111111111111112</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-5.050000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1715936119605844</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
